--- a/docs/source/figures/Material_Database_Overview.xlsx
+++ b/docs/source/figures/Material_Database_Overview.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_Repositorys\materialdatabase\docs\source\figures\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tpiepe\Repositories\materialdatabase\docs\source\figures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A6DD5A-90E3-4FE5-8F46-34205D0BF8D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C7B31BD-3FBD-4CC0-A39E-8D2A041515F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E51A1F85-B08D-41FE-9B94-BB5FD5A5BD95}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E51A1F85-B08D-41FE-9B94-BB5FD5A5BD95}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="before_2026_05_08" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,15 +30,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="58">
   <si>
     <t>Material</t>
   </si>
@@ -340,12 +338,136 @@
   <si>
     <t>TDK_MDT</t>
   </si>
+  <si>
+    <t>LEA MTB</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>µ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> at 25°C</t>
+    </r>
+  </si>
+  <si>
+    <t>Further Information</t>
+  </si>
+  <si>
+    <r>
+      <t>Complex Permeability
+µ(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>f</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, |</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>B|</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Complex 
+Permittivity
+ε(f, T)</t>
+  </si>
+  <si>
+    <t>How to generate the image for the readme:
+1. select the table area
+2. Home-&gt;Copy-&gt;Copy as Picture -&gt; as shown when printed
+3. Paste into spreadsheet
+4. Save as Picture -&gt; choose jpg to have white backrgound!</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -413,6 +535,61 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <vertAlign val="subscript"/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF92D050"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -434,7 +611,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="48">
     <border>
       <left/>
       <right/>
@@ -668,11 +845,404 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -768,9 +1338,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -810,25 +1377,28 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -843,24 +1413,172 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1199,34 +1917,417 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F83654C4-16D0-484A-BE01-4B99138EE44B}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:R22"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="2.85546875" customWidth="1"/>
+    <col min="11" max="11" width="16.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="62"/>
+      <c r="B1" s="103" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="104"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="108" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="106" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
+      <c r="I1" s="107"/>
+    </row>
+    <row r="2" spans="1:18" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="87" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="88" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="86" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="89" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="90" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="91" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="86" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="92" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="93" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" s="110" t="s">
+        <v>57</v>
+      </c>
+      <c r="N2" s="110"/>
+      <c r="O2" s="110"/>
+      <c r="P2" s="110"/>
+      <c r="Q2" s="110"/>
+      <c r="R2" s="109"/>
+    </row>
+    <row r="3" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="82" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="83"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="102" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="85">
+        <v>3000</v>
+      </c>
+      <c r="H3" s="85" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="95" t="s">
+        <v>6</v>
+      </c>
+      <c r="M3" s="110"/>
+      <c r="N3" s="110"/>
+      <c r="O3" s="110"/>
+      <c r="P3" s="110"/>
+      <c r="Q3" s="110"/>
+      <c r="R3" s="109"/>
+    </row>
+    <row r="4" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="67"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="100"/>
+      <c r="G4" s="66">
+        <v>2200</v>
+      </c>
+      <c r="H4" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="96"/>
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110"/>
+      <c r="P4" s="110"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="109"/>
+    </row>
+    <row r="5" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="78" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="67"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="66">
+        <v>1500</v>
+      </c>
+      <c r="H5" s="66" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="96"/>
+      <c r="M5" s="110"/>
+      <c r="N5" s="110"/>
+      <c r="O5" s="110"/>
+      <c r="P5" s="110"/>
+      <c r="Q5" s="110"/>
+      <c r="R5" s="109"/>
+    </row>
+    <row r="6" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="78" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="67"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="100"/>
+      <c r="G6" s="66">
+        <v>800</v>
+      </c>
+      <c r="H6" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="96"/>
+      <c r="M6" s="109"/>
+      <c r="N6" s="109"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="109"/>
+      <c r="R6" s="109"/>
+    </row>
+    <row r="7" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="78" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="70"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="101"/>
+      <c r="G7" s="66">
+        <v>2000</v>
+      </c>
+      <c r="H7" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="96"/>
+      <c r="M7" s="109"/>
+      <c r="N7" s="109"/>
+      <c r="O7" s="109"/>
+      <c r="P7" s="109"/>
+      <c r="Q7" s="109"/>
+      <c r="R7" s="109"/>
+    </row>
+    <row r="8" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="78" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="70"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="99" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" s="66">
+        <v>4300</v>
+      </c>
+      <c r="H8" s="66" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="96"/>
+    </row>
+    <row r="9" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="78" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="70"/>
+      <c r="C9" s="63"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="101"/>
+      <c r="G9" s="66">
+        <v>6500</v>
+      </c>
+      <c r="H9" s="66" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="94"/>
+    </row>
+    <row r="10" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="78" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="70"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="99" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="66">
+        <v>750</v>
+      </c>
+      <c r="H10" s="66" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="97" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="78" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="70"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="74"/>
+      <c r="F11" s="100"/>
+      <c r="G11" s="66">
+        <v>2300</v>
+      </c>
+      <c r="H11" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="96"/>
+    </row>
+    <row r="12" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="78" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="70"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="74"/>
+      <c r="F12" s="100"/>
+      <c r="G12" s="66">
+        <v>1800</v>
+      </c>
+      <c r="H12" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" s="96"/>
+    </row>
+    <row r="13" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="78" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="70"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="100"/>
+      <c r="G13" s="66">
+        <v>2300</v>
+      </c>
+      <c r="H13" s="66" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" s="96"/>
+    </row>
+    <row r="14" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="78" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="70"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="68"/>
+      <c r="E14" s="74"/>
+      <c r="F14" s="100"/>
+      <c r="G14" s="66">
+        <v>3000</v>
+      </c>
+      <c r="H14" s="66" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="96"/>
+    </row>
+    <row r="15" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="78" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="70"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="68"/>
+      <c r="E15" s="74"/>
+      <c r="F15" s="101"/>
+      <c r="G15" s="66">
+        <v>900</v>
+      </c>
+      <c r="H15" s="66" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="96"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+    </row>
+    <row r="16" spans="1:18" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="79" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="71"/>
+      <c r="C16" s="72"/>
+      <c r="D16" s="73"/>
+      <c r="E16" s="77"/>
+      <c r="F16" s="80" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="81">
+        <v>10000</v>
+      </c>
+      <c r="H16" s="81" t="s">
+        <v>20</v>
+      </c>
+      <c r="I16" s="98"/>
+    </row>
+    <row r="17" spans="1:1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="1:1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="M2:Q5"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="I3:I9"/>
+    <mergeCell ref="I10:I16"/>
+    <mergeCell ref="F10:F15"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="F3:F7"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="61" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="A16" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54C0E5B5-18E2-4E4E-9F25-E5DE0C61951C}">
   <dimension ref="A1:O23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.75" customWidth="1"/>
-    <col min="2" max="2" width="13.75" customWidth="1"/>
-    <col min="3" max="3" width="20.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="14" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.375" customWidth="1"/>
+    <col min="8" max="8" width="25.42578125" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="25.75" customWidth="1"/>
+    <col min="10" max="10" width="25.7109375" customWidth="1"/>
     <col min="11" max="11" width="17" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="2.875" customWidth="1"/>
-    <col min="13" max="13" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="2.85546875" customWidth="1"/>
+    <col min="13" max="13" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="21" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="52" t="s">
+    <row r="1" spans="1:15" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="51" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="33" t="s">
         <v>51</v>
       </c>
       <c r="E1" s="56" t="s">
@@ -1245,44 +2346,44 @@
       <c r="J1" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="52" t="s">
+      <c r="K1" s="51" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="21" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="53"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="35" t="s">
+    <row r="2" spans="1:15" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="52"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="35" t="s">
+      <c r="D2" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="35" t="s">
+      <c r="E2" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="35" t="s">
+      <c r="F2" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="35" t="s">
+      <c r="G2" s="34" t="s">
         <v>48</v>
       </c>
       <c r="H2" s="55"/>
       <c r="I2" s="56"/>
       <c r="J2" s="57"/>
-      <c r="K2" s="53"/>
-    </row>
-    <row r="3" spans="1:15" ht="25.5" customHeight="1" thickTop="1" thickBot="1">
+      <c r="K2" s="52"/>
+    </row>
+    <row r="3" spans="1:15" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="37"/>
+      <c r="B3" s="36"/>
       <c r="C3" s="18"/>
       <c r="D3" s="18"/>
       <c r="E3" s="25"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="50" t="s">
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="60" t="s">
         <v>26</v>
       </c>
       <c r="I3" s="10">
@@ -1291,30 +2392,30 @@
       <c r="J3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="48" t="s">
+      <c r="K3" s="53" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="25.5" customHeight="1" thickTop="1" thickBot="1">
+    <row r="4" spans="1:15" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="50"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="60"/>
       <c r="I4" s="11">
         <v>2200</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K4" s="48"/>
-    </row>
-    <row r="5" spans="1:15" ht="25.5" customHeight="1" thickTop="1" thickBot="1">
+      <c r="K4" s="53"/>
+    </row>
+    <row r="5" spans="1:15" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="22" t="s">
         <v>32</v>
       </c>
@@ -1323,36 +2424,36 @@
       <c r="D5" s="30"/>
       <c r="E5" s="29"/>
       <c r="F5" s="29"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="50"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="60"/>
       <c r="I5" s="11">
         <v>1500</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="48"/>
-    </row>
-    <row r="6" spans="1:15" ht="25.5" customHeight="1" thickTop="1" thickBot="1">
+      <c r="K5" s="53"/>
+    </row>
+    <row r="6" spans="1:15" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="50"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="60"/>
       <c r="I6" s="11">
         <v>800</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K6" s="48"/>
-    </row>
-    <row r="7" spans="1:15" ht="25.5" customHeight="1" thickTop="1" thickBot="1">
+      <c r="K6" s="53"/>
+    </row>
+    <row r="7" spans="1:15" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="22" t="s">
         <v>34</v>
       </c>
@@ -1361,27 +2462,27 @@
       <c r="D7" s="19"/>
       <c r="E7" s="27"/>
       <c r="F7" s="30"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="50"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="60"/>
       <c r="I7" s="16">
         <v>2000</v>
       </c>
       <c r="J7" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="K7" s="48"/>
-    </row>
-    <row r="8" spans="1:15" ht="25.5" customHeight="1" thickTop="1" thickBot="1">
+      <c r="K7" s="53"/>
+    </row>
+    <row r="8" spans="1:15" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="50" t="s">
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="47"/>
+      <c r="H8" s="60" t="s">
         <v>28</v>
       </c>
       <c r="I8" s="13">
@@ -1390,29 +2491,29 @@
       <c r="J8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="K8" s="48"/>
-    </row>
-    <row r="9" spans="1:15" ht="25.5" customHeight="1" thickTop="1" thickBot="1">
+      <c r="K8" s="53"/>
+    </row>
+    <row r="9" spans="1:15" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="39"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="40"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="61"/>
-      <c r="H9" s="50"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="60"/>
       <c r="I9" s="16">
         <v>6500</v>
       </c>
       <c r="J9" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="K9" s="48"/>
-    </row>
-    <row r="10" spans="1:15" ht="25.5" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="33" t="s">
+      <c r="K9" s="53"/>
+    </row>
+    <row r="10" spans="1:15" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
         <v>37</v>
       </c>
       <c r="B10" s="24"/>
@@ -1421,7 +2522,7 @@
       <c r="E10" s="26"/>
       <c r="F10" s="26"/>
       <c r="G10" s="26"/>
-      <c r="H10" s="36" t="s">
+      <c r="H10" s="35" t="s">
         <v>25</v>
       </c>
       <c r="I10" s="14">
@@ -1434,17 +2535,17 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="25.5" customHeight="1" thickTop="1" thickBot="1">
+    <row r="11" spans="1:15" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="37"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
       <c r="E11" s="25"/>
-      <c r="F11" s="38"/>
+      <c r="F11" s="37"/>
       <c r="G11" s="25"/>
-      <c r="H11" s="50" t="s">
+      <c r="H11" s="60" t="s">
         <v>25</v>
       </c>
       <c r="I11" s="13">
@@ -1453,30 +2554,30 @@
       <c r="J11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="K11" s="47" t="s">
+      <c r="K11" s="58" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="25.5" customHeight="1" thickTop="1" thickBot="1">
+    <row r="12" spans="1:15" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="50"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="60"/>
       <c r="I12" s="11">
         <v>2300</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K12" s="48"/>
-    </row>
-    <row r="13" spans="1:15" ht="25.5" customHeight="1" thickTop="1" thickBot="1">
+      <c r="K12" s="53"/>
+    </row>
+    <row r="13" spans="1:15" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="22" t="s">
         <v>40</v>
       </c>
@@ -1486,35 +2587,35 @@
       <c r="E13" s="27"/>
       <c r="F13" s="29"/>
       <c r="G13" s="29"/>
-      <c r="H13" s="50"/>
+      <c r="H13" s="60"/>
       <c r="I13" s="11">
         <v>1800</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K13" s="48"/>
-    </row>
-    <row r="14" spans="1:15" ht="25.5" customHeight="1" thickTop="1" thickBot="1">
+      <c r="K13" s="53"/>
+    </row>
+    <row r="14" spans="1:15" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="50"/>
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="60"/>
       <c r="I14" s="11">
         <v>2300</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K14" s="48"/>
-    </row>
-    <row r="15" spans="1:15" ht="25.5" customHeight="1" thickTop="1" thickBot="1">
+      <c r="K14" s="53"/>
+    </row>
+    <row r="15" spans="1:15" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="22" t="s">
         <v>42</v>
       </c>
@@ -1524,47 +2625,47 @@
       <c r="E15" s="27"/>
       <c r="F15" s="29"/>
       <c r="G15" s="29"/>
-      <c r="H15" s="50"/>
+      <c r="H15" s="60"/>
       <c r="I15" s="11">
         <v>3000</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K15" s="48"/>
-    </row>
-    <row r="16" spans="1:15" ht="25.5" customHeight="1" thickTop="1" thickBot="1">
+      <c r="K15" s="53"/>
+    </row>
+    <row r="16" spans="1:15" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="50"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="60"/>
       <c r="I16" s="12">
         <v>900</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K16" s="48"/>
+      <c r="K16" s="53"/>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
     </row>
-    <row r="17" spans="1:11" ht="25.5" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A17" s="45" t="s">
+    <row r="17" spans="1:11" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="39"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="36" t="s">
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="50"/>
+      <c r="H17" s="35" t="s">
         <v>29</v>
       </c>
       <c r="I17" s="6">
@@ -1573,19 +2674,19 @@
       <c r="J17" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="K17" s="48"/>
-    </row>
-    <row r="18" spans="1:11" ht="25.5" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A18" s="46">
+      <c r="K17" s="53"/>
+    </row>
+    <row r="18" spans="1:11" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="45">
         <v>77</v>
       </c>
-      <c r="B18" s="37"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
       <c r="E18" s="25"/>
       <c r="F18" s="25"/>
       <c r="G18" s="25"/>
-      <c r="H18" s="51" t="s">
+      <c r="H18" s="61" t="s">
         <v>25</v>
       </c>
       <c r="I18" s="13">
@@ -1594,50 +2695,50 @@
       <c r="J18" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="K18" s="49" t="s">
+      <c r="K18" s="59" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="25.5" customHeight="1" thickTop="1" thickBot="1">
+    <row r="19" spans="1:11" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="23">
         <v>78</v>
       </c>
-      <c r="B19" s="41"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="51"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="61"/>
       <c r="I19" s="11">
         <v>2300</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K19" s="49"/>
-    </row>
-    <row r="20" spans="1:11" ht="25.5" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A20" s="45">
+      <c r="K19" s="59"/>
+    </row>
+    <row r="20" spans="1:11" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="44">
         <v>79</v>
       </c>
-      <c r="B20" s="39"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="51"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="61"/>
       <c r="I20" s="12">
         <v>1400</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="K20" s="49"/>
-    </row>
-    <row r="21" spans="1:11" ht="25.5" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A21" s="33" t="s">
+      <c r="K20" s="59"/>
+    </row>
+    <row r="21" spans="1:11" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
         <v>45</v>
       </c>
       <c r="B21" s="24"/>
@@ -1646,7 +2747,7 @@
       <c r="E21" s="26"/>
       <c r="F21" s="26"/>
       <c r="G21" s="26"/>
-      <c r="H21" s="51"/>
+      <c r="H21" s="61"/>
       <c r="I21" s="6">
         <v>1100</v>
       </c>
@@ -1657,34 +2758,29 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15" thickTop="1">
+    <row r="22" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="H18:H21"/>
+    <mergeCell ref="K18:K20"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="H3:H7"/>
+    <mergeCell ref="K3:K9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="H11:H16"/>
+    <mergeCell ref="K11:K17"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="K3:K9"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="K11:K17"/>
-    <mergeCell ref="K18:K20"/>
-    <mergeCell ref="H3:H7"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="H11:H16"/>
-    <mergeCell ref="H18:H21"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="A17" numberStoredAsText="1"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>